--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,415 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130261101</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93004</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flygstaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>613228</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6793976</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130261204</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93010</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flygstaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>613228</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6793976</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Hedtallskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130261109</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93026</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flygstaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>613228</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6793976</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130261097</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flygstaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>613228</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6793976</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93004</v>
+        <v>93007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93026</v>
+        <v>93029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93035</v>
+        <v>93038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93007</v>
+        <v>93033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93029</v>
+        <v>93055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93038</v>
+        <v>93064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93033</v>
+        <v>93034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93055</v>
+        <v>93056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93064</v>
+        <v>93065</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93034</v>
+        <v>93035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93056</v>
+        <v>93057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93065</v>
+        <v>93066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93035</v>
+        <v>93037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93066</v>
+        <v>93068</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93037</v>
+        <v>93041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93059</v>
+        <v>93063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93068</v>
+        <v>93072</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -2637,7 +2637,7 @@
         <v>130261101</v>
       </c>
       <c r="B19" t="n">
-        <v>93041</v>
+        <v>93054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130261204</v>
       </c>
       <c r="B20" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>130261109</v>
       </c>
       <c r="B21" t="n">
-        <v>93063</v>
+        <v>93076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>130261097</v>
       </c>
       <c r="B22" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51147-2025 artfynd.xlsx
+++ b/artfynd/A 51147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61909952</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261101</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261204</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111018136</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102169582</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,8 +1581,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79787202</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>